--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.25095604556662</v>
+        <v>8.328280357404577</v>
       </c>
       <c r="D2" t="n">
-        <v>51.09846716708394</v>
+        <v>8.30350091465114</v>
       </c>
       <c r="E2" t="n">
-        <v>9.802878551901697</v>
+        <v>1.592967764684026</v>
       </c>
       <c r="F2" t="n">
-        <v>8.858556465727379</v>
+        <v>1.439515425680699</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.82752939679864</v>
+        <v>8.421973526979778</v>
       </c>
       <c r="D3" t="n">
-        <v>41.33676560884896</v>
+        <v>6.717224411437956</v>
       </c>
       <c r="E3" t="n">
-        <v>9.802878551901697</v>
+        <v>1.592967764684026</v>
       </c>
       <c r="F3" t="n">
-        <v>8.858556465727379</v>
+        <v>1.439515425680699</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.47166234862993</v>
+        <v>9.989145131652364</v>
       </c>
       <c r="D4" t="n">
-        <v>55.10866830505424</v>
+        <v>8.955158599571314</v>
       </c>
       <c r="E4" t="n">
-        <v>9.802878551901697</v>
+        <v>1.592967764684026</v>
       </c>
       <c r="F4" t="n">
-        <v>8.858556465727379</v>
+        <v>1.439515425680699</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>75.45590129419901</v>
+        <v>12.26158396030734</v>
       </c>
       <c r="D5" t="n">
-        <v>32.3072514156067</v>
+        <v>5.249928355036089</v>
       </c>
       <c r="E5" t="n">
-        <v>9.802878551901697</v>
+        <v>1.592967764684026</v>
       </c>
       <c r="F5" t="n">
-        <v>8.858556465727379</v>
+        <v>1.439515425680699</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
